--- a/tiflow-erezept/fhir-error-codes/1.0.0-draft/ValueSet-tiflow-erezept-operation-outcome-details-vs.xlsx
+++ b/tiflow-erezept/fhir-error-codes/1.0.0-draft/ValueSet-tiflow-erezept-operation-outcome-details-vs.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="97">
   <si>
     <t>Property</t>
   </si>
@@ -119,97 +119,190 @@
     <t>TIFLOW_AUTH_ROLE_NOT_ALLOWED</t>
   </si>
   <si>
+    <t>Access role not allowed</t>
+  </si>
+  <si>
     <t>TIFLOW_SECRET_MISMATCH</t>
   </si>
   <si>
+    <t>Task secret mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_STATUS_MISMATCH</t>
   </si>
   <si>
+    <t>Task status mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_MEDICATION_DISPENSE_INVALID</t>
   </si>
   <si>
+    <t>MedicationDispense invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_MEDICATION_DISPENSE_MISSING</t>
   </si>
   <si>
+    <t>MedicationDispense missing</t>
+  </si>
+  <si>
     <t>TIFLOW_SIGNATURE_NO_OCSP_RESPONSE</t>
   </si>
   <si>
+    <t>No OCSP response for signature</t>
+  </si>
+  <si>
     <t>TIFLOW_AUTH_NOT_OWNER</t>
   </si>
   <si>
+    <t>Authenticated actor is not owner</t>
+  </si>
+  <si>
     <t>TIFLOW_ACCESSCODE_MISMATCH</t>
   </si>
   <si>
+    <t>Access code mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_ID_REQUIRED</t>
   </si>
   <si>
+    <t>Task id required</t>
+  </si>
+  <si>
     <t>TIFLOW_KVNR_MISMATCH</t>
   </si>
   <si>
+    <t>KVNR mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_SIGNATURE_INVALID_ISSUING_ROLE</t>
   </si>
   <si>
+    <t>Signature issuing role invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_FLOWTYPE_MISMATCH</t>
   </si>
   <si>
+    <t>Flow type mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_COVERAGE_TYPE_MISMATCH</t>
   </si>
   <si>
+    <t>Coverage type mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_CERTIFICATE_INVALID</t>
   </si>
   <si>
+    <t>Certificate invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_OCSP_BACKEND_ERROR</t>
   </si>
   <si>
+    <t>Invalid OCSP response</t>
+  </si>
+  <si>
     <t>TIFLOW_SIGNATURE_INVALID</t>
   </si>
   <si>
+    <t>Signature invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_KVNR_INVALID</t>
   </si>
   <si>
+    <t>KVNR invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_SIGNATURE_AUTHOREDON_MISMATCH</t>
   </si>
   <si>
+    <t>Signature authoredOn mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_IKNR_INVALID</t>
   </si>
   <si>
+    <t>IKNR invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_LANR_ZANR_INVALID</t>
   </si>
   <si>
+    <t>LANR or ZANR invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_DELETED</t>
   </si>
   <si>
+    <t>Task deleted</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_EXPIRED</t>
   </si>
   <si>
+    <t>Task expired</t>
+  </si>
+  <si>
     <t>TIFLOW_MESSAGE_TO_SELF</t>
   </si>
   <si>
+    <t>Message to self not allowed</t>
+  </si>
+  <si>
     <t>TIFLOW_COMMUNICATION_PAYLOAD_INVALID</t>
   </si>
   <si>
+    <t>Communication payload invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_INSURANT_NOT_ELIGIBLE</t>
   </si>
   <si>
+    <t>Insurant not eligible</t>
+  </si>
+  <si>
     <t>TIFLOW_RECIPIENT_INVALID</t>
   </si>
   <si>
+    <t>Recipient invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_NOT_FOUND</t>
   </si>
   <si>
+    <t>Task not found</t>
+  </si>
+  <si>
     <t>TIFLOW_MVO_NOT_VALID_YET</t>
   </si>
   <si>
+    <t>MVO not valid yet</t>
+  </si>
+  <si>
     <t>https://gematik.de/fhir/tiflow/core/CodeSystem/tiflow-operation-outcome-details-cs</t>
   </si>
   <si>
     <t>SVC_VALIDATION_FAILED</t>
   </si>
   <si>
+    <t>FHIR Profile Validation Failed</t>
+  </si>
+  <si>
     <t>SVC_IDENTITY_MISMATCH</t>
   </si>
   <si>
+    <t>Identity mismatch: Access token or x-insurantid header does not match FHIR data (Telematik-ID / KVNR)</t>
+  </si>
+  <si>
     <t>SVC_TELEMATIKID_TEMPORARILY_BLOCKED</t>
+  </si>
+  <si>
+    <t>The specified Telematik-ID is temporarily blocked</t>
   </si>
   <si>
     <t>https://gematik.de/fhir/ti/CodeSystem/operation-outcome-details-codes</t>
@@ -533,169 +626,225 @@
       <c r="A2" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B16" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B17" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B18" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B19" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B21" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B22" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B23" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B24" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B25" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B26" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B27" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B28" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>86</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B29" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>88</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
@@ -710,7 +859,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -737,21 +886,27 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>91</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>93</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -766,7 +921,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>65</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
